--- a/ws2/files/WS2_Mock_Run_Scorecard.xlsx
+++ b/ws2/files/WS2_Mock_Run_Scorecard.xlsx
@@ -1159,7 +1159,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Trap test run and the result recorded (kit-specific)</t>
+          <t>Time test run and hours back per PM per week recorded (kit-specific)</t>
         </is>
       </c>
       <c r="C18" s="11" t="n"/>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Trap test run and the result recorded (kit-specific)</t>
+          <t>Time test run and hours back per PM per week recorded (kit-specific)</t>
         </is>
       </c>
       <c r="C18" s="11" t="n"/>

--- a/ws2/files/WS2_Mock_Run_Scorecard.xlsx
+++ b/ws2/files/WS2_Mock_Run_Scorecard.xlsx
@@ -559,7 +559,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Pain to Pilot kit · draft v0.1 · one workbook per mock run, shared by all observers</t>
+          <t>Pain to Pilot kit · draft v0.2 · one workbook per mock run, shared by all observers</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>One scorecard per room: 12 items scored 1–5 with the minute and the evidence, plus the six pass criteria (Yes / No).</t>
+          <t>One scorecard per room: 13 items scored 1–5 with the minute and the evidence, plus the seven pass criteria (Yes / No).</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>D01 · Room A · Frame the pain · Room debated whether status reports are a real pain until minute 11 · S2 · Card does not say the pain is given · Add “the pain is given; choose the slice” to the Orient script · WS2 · Retest at facilitator dry run · Open</t>
+          <t>D01 · Room A · Map the hours · Room debated whether risk-log upkeep is a real pain until minute 11 · S2 · Card does not say the pain is given · Add “the pain is given; choose the slice” to the Orient script · WS2 · Retest at facilitator dry run · Open</t>
         </is>
       </c>
     </row>
@@ -755,15 +755,15 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Items scored (of 12)</t>
+          <t>Items scored (of 13)</t>
         </is>
       </c>
       <c r="B5" s="8">
-        <f>'Room A'!C21</f>
+        <f>'Room A'!C22</f>
         <v/>
       </c>
       <c r="C5" s="8">
-        <f>'Room B'!C21</f>
+        <f>'Room B'!C22</f>
         <v/>
       </c>
     </row>
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="B6" s="9">
-        <f>'Room A'!C22</f>
+        <f>'Room A'!C23</f>
         <v/>
       </c>
       <c r="C6" s="9">
-        <f>'Room B'!C22</f>
+        <f>'Room B'!C23</f>
         <v/>
       </c>
     </row>
@@ -789,11 +789,11 @@
         </is>
       </c>
       <c r="B7" s="8">
-        <f>'Room A'!C23</f>
+        <f>'Room A'!C24</f>
         <v/>
       </c>
       <c r="C7" s="8">
-        <f>'Room B'!C23</f>
+        <f>'Room B'!C24</f>
         <v/>
       </c>
     </row>
@@ -804,11 +804,11 @@
         </is>
       </c>
       <c r="B8" s="8">
-        <f>'Room A'!C24</f>
+        <f>'Room A'!C25</f>
         <v/>
       </c>
       <c r="C8" s="8">
-        <f>'Room B'!C24</f>
+        <f>'Room B'!C25</f>
         <v/>
       </c>
     </row>
@@ -819,11 +819,11 @@
         </is>
       </c>
       <c r="B9" s="8">
-        <f>'Room A'!C34</f>
+        <f>'Room A'!C36</f>
         <v/>
       </c>
       <c r="C9" s="8">
-        <f>'Room B'!C34</f>
+        <f>'Room B'!C36</f>
         <v/>
       </c>
     </row>
@@ -834,11 +834,11 @@
         </is>
       </c>
       <c r="B10" s="8">
-        <f>COUNTIF('Timing log'!F5:F10,"&gt;3")</f>
+        <f>COUNTIF('Timing log'!F5:F11,"&gt;3")</f>
         <v/>
       </c>
       <c r="C10" s="8">
-        <f>COUNTIF('Timing log'!H5:H10,"&gt;3")</f>
+        <f>COUNTIF('Timing log'!H5:H11,"&gt;3")</f>
         <v/>
       </c>
     </row>
@@ -948,7 +948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -968,7 +968,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Card C1 Status Report Treadmill, given · experienced facilitator · 7–8 participants · approved tool available</t>
+          <t>Card C3 The Silent Risk, given · experienced facilitator · 7–8 participants · approved tool available</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Report-out completed within the limit</t>
+          <t>Debrief card delivered within the limit</t>
         </is>
       </c>
       <c r="C17" s="11" t="n"/>
@@ -1172,99 +1172,100 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Room recovered from each injected failure without observer help (kit-specific)</t>
+          <t>Business impact and failure mode named; guardrail written against the failure (kit-specific)</t>
         </is>
       </c>
       <c r="C19" s="11" t="n"/>
       <c r="D19" s="11" t="n"/>
       <c r="E19" s="11" t="n"/>
     </row>
-    <row r="21">
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Items scored</t>
-        </is>
-      </c>
-      <c r="C21" s="12">
-        <f>COUNT(C8:C19)</f>
-        <v/>
-      </c>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Room recovered from each injected failure without observer help (kit-specific)</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="n"/>
+      <c r="D20" s="11" t="n"/>
+      <c r="E20" s="11" t="n"/>
     </row>
     <row r="22">
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Average score</t>
-        </is>
-      </c>
-      <c r="C22" s="13">
-        <f>IF(COUNT(C8:C19)=0,"",AVERAGE(C8:C19))</f>
+          <t>Items scored</t>
+        </is>
+      </c>
+      <c r="C22" s="12">
+        <f>COUNT(C8:C20)</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Items scored 1</t>
-        </is>
-      </c>
-      <c r="C23" s="12">
-        <f>COUNTIF(C8:C19,1)</f>
+          <t>Average score</t>
+        </is>
+      </c>
+      <c r="C23" s="13">
+        <f>IF(COUNT(C8:C20)=0,"",AVERAGE(C8:C20))</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="3" t="inlineStr">
         <is>
+          <t>Items scored 1</t>
+        </is>
+      </c>
+      <c r="C24" s="12">
+        <f>COUNTIF(C8:C20,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="3" t="inlineStr">
+        <is>
           <t>Meets score bar (avg ≥ 3.5, no 1s)</t>
         </is>
       </c>
-      <c r="C24" s="12">
-        <f>IF(C21&lt;12,"Incomplete",IF(AND(C22&gt;=3.5,C23=0),"Yes","No"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="C25" s="12">
+        <f>IF(C22&lt;13,"Incomplete",IF(AND(C23&gt;=3.5,C24=0),"Yes","No"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>Pass criterion</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr"/>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr"/>
+      <c r="E27" s="6" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>100% of the ten mandatory Pilot Pack fields completed</t>
-        </is>
-      </c>
-      <c r="C27" s="11" t="n"/>
-      <c r="E27" s="11" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Owner, first test, metric and guardrail explicit</t>
+          <t>100% of the fourteen mandatory Pilot Pack fields completed</t>
         </is>
       </c>
       <c r="C28" s="11" t="n"/>
@@ -1272,11 +1273,11 @@
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Facilitator did not need content expertise to finish</t>
+          <t>Owner, first test, hours back, business impact and a guardrail against a named failure explicit</t>
         </is>
       </c>
       <c r="C29" s="11" t="n"/>
@@ -1284,11 +1285,11 @@
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Someone outside the room can read the pack in 3 minutes and restate it</t>
+          <t>Compressed Summit Debrief names Monday Morning Pilot, Most Hours Back and Strongest Guardrail</t>
         </is>
       </c>
       <c r="C30" s="11" t="n"/>
@@ -1296,11 +1297,11 @@
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>No unresolved confidentiality or tool-approval issue hidden</t>
+          <t>Facilitator did not need content expertise to finish</t>
         </is>
       </c>
       <c r="C31" s="11" t="n"/>
@@ -1308,34 +1309,58 @@
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Final recommendation produced inside the 60-minute slot</t>
+          <t>Someone outside the room can read the pack in 3 minutes and restate it</t>
         </is>
       </c>
       <c r="C32" s="11" t="n"/>
       <c r="E32" s="11" t="n"/>
     </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>No unresolved confidentiality or tool-approval issue hidden</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="n"/>
+      <c r="E33" s="11" t="n"/>
+    </row>
     <row r="34">
-      <c r="B34" s="3" t="inlineStr">
+      <c r="A34" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Final recommendation produced inside the 60-minute slot</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="n"/>
+      <c r="E34" s="11" t="n"/>
+    </row>
+    <row r="36">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>Pass criteria result</t>
         </is>
       </c>
-      <c r="C34" s="12">
-        <f>IF(COUNTA(C27:C32)&lt;6,"Incomplete",IF(COUNTIF(C27:C32,"Yes")=6,"Pass","Fail"))</f>
+      <c r="C36" s="12">
+        <f>IF(COUNTA(C28:C34)&lt;7,"Incomplete",IF(COUNTIF(C28:C34,"Yes")=7,"Pass","Fail"))</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" error="Enter a whole number from 1 to 5." type="whole" operator="between">
+    <dataValidation sqref="C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" error="Enter a whole number from 1 to 5." type="whole" operator="between">
       <formula1>1</formula1>
       <formula2>5</formula2>
     </dataValidation>
-    <dataValidation sqref="C27 C28 C29 C30 C31 C32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C28 C29 C30 C31 C32 C33 C34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1349,7 +1374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1547,7 +1572,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Report-out completed within the limit</t>
+          <t>Debrief card delivered within the limit</t>
         </is>
       </c>
       <c r="C17" s="11" t="n"/>
@@ -1573,99 +1598,100 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Room recovered from each injected failure without observer help (kit-specific)</t>
+          <t>Business impact and failure mode named; guardrail written against the failure (kit-specific)</t>
         </is>
       </c>
       <c r="C19" s="11" t="n"/>
       <c r="D19" s="11" t="n"/>
       <c r="E19" s="11" t="n"/>
     </row>
-    <row r="21">
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Items scored</t>
-        </is>
-      </c>
-      <c r="C21" s="12">
-        <f>COUNT(C8:C19)</f>
-        <v/>
-      </c>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Room recovered from each injected failure without observer help (kit-specific)</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="n"/>
+      <c r="D20" s="11" t="n"/>
+      <c r="E20" s="11" t="n"/>
     </row>
     <row r="22">
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Average score</t>
-        </is>
-      </c>
-      <c r="C22" s="13">
-        <f>IF(COUNT(C8:C19)=0,"",AVERAGE(C8:C19))</f>
+          <t>Items scored</t>
+        </is>
+      </c>
+      <c r="C22" s="12">
+        <f>COUNT(C8:C20)</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Items scored 1</t>
-        </is>
-      </c>
-      <c r="C23" s="12">
-        <f>COUNTIF(C8:C19,1)</f>
+          <t>Average score</t>
+        </is>
+      </c>
+      <c r="C23" s="13">
+        <f>IF(COUNT(C8:C20)=0,"",AVERAGE(C8:C20))</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="3" t="inlineStr">
         <is>
+          <t>Items scored 1</t>
+        </is>
+      </c>
+      <c r="C24" s="12">
+        <f>COUNTIF(C8:C20,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="3" t="inlineStr">
+        <is>
           <t>Meets score bar (avg ≥ 3.5, no 1s)</t>
         </is>
       </c>
-      <c r="C24" s="12">
-        <f>IF(C21&lt;12,"Incomplete",IF(AND(C22&gt;=3.5,C23=0),"Yes","No"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="C25" s="12">
+        <f>IF(C22&lt;13,"Incomplete",IF(AND(C23&gt;=3.5,C24=0),"Yes","No"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>Pass criterion</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr"/>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr"/>
+      <c r="E27" s="6" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>100% of the ten mandatory Pilot Pack fields completed</t>
-        </is>
-      </c>
-      <c r="C27" s="11" t="n"/>
-      <c r="E27" s="11" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Owner, first test, metric and guardrail explicit</t>
+          <t>100% of the fourteen mandatory Pilot Pack fields completed</t>
         </is>
       </c>
       <c r="C28" s="11" t="n"/>
@@ -1673,11 +1699,11 @@
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Facilitator did not need content expertise to finish</t>
+          <t>Owner, first test, hours back, business impact and a guardrail against a named failure explicit</t>
         </is>
       </c>
       <c r="C29" s="11" t="n"/>
@@ -1685,11 +1711,11 @@
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Someone outside the room can read the pack in 3 minutes and restate it</t>
+          <t>Compressed Summit Debrief names Monday Morning Pilot, Most Hours Back and Strongest Guardrail</t>
         </is>
       </c>
       <c r="C30" s="11" t="n"/>
@@ -1697,11 +1723,11 @@
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>No unresolved confidentiality or tool-approval issue hidden</t>
+          <t>Facilitator did not need content expertise to finish</t>
         </is>
       </c>
       <c r="C31" s="11" t="n"/>
@@ -1709,34 +1735,58 @@
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Final recommendation produced inside the 60-minute slot</t>
+          <t>Someone outside the room can read the pack in 3 minutes and restate it</t>
         </is>
       </c>
       <c r="C32" s="11" t="n"/>
       <c r="E32" s="11" t="n"/>
     </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>No unresolved confidentiality or tool-approval issue hidden</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="n"/>
+      <c r="E33" s="11" t="n"/>
+    </row>
     <row r="34">
-      <c r="B34" s="3" t="inlineStr">
+      <c r="A34" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Final recommendation produced inside the 60-minute slot</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="n"/>
+      <c r="E34" s="11" t="n"/>
+    </row>
+    <row r="36">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>Pass criteria result</t>
         </is>
       </c>
-      <c r="C34" s="12">
-        <f>IF(COUNTA(C27:C32)&lt;6,"Incomplete",IF(COUNTIF(C27:C32,"Yes")=6,"Pass","Fail"))</f>
+      <c r="C36" s="12">
+        <f>IF(COUNTA(C28:C34)&lt;7,"Incomplete",IF(COUNTIF(C28:C34,"Yes")=7,"Pass","Fail"))</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" error="Enter a whole number from 1 to 5." type="whole" operator="between">
+    <dataValidation sqref="C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" error="Enter a whole number from 1 to 5." type="whole" operator="between">
       <formula1>1</formula1>
       <formula2>5</formula2>
     </dataValidation>
-    <dataValidation sqref="C27 C28 C29 C30 C31 C32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C28 C29 C30 C31 C32 C33 C34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1750,7 +1800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1849,7 +1899,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Frame the pain</t>
+          <t>Map the hours</t>
         </is>
       </c>
       <c r="B6" s="14" t="n">
@@ -1981,28 +2031,55 @@
         <v/>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Summit Debrief, compressed</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="C11" s="14" t="n">
+        <v>65</v>
+      </c>
+      <c r="D11" s="15">
+        <f>C11-B11</f>
+        <v/>
+      </c>
+      <c r="E11" s="16" t="n"/>
+      <c r="F11" s="15">
+        <f>IF(E11="","",E11-C11)</f>
+        <v/>
+      </c>
+      <c r="G11" s="16" t="n"/>
+      <c r="H11" s="15">
+        <f>IF(G11="","",G11-C11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Room B: minute the card was chosen</t>
         </is>
       </c>
-      <c r="E12" s="17" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="E13" s="17" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Planned stage times come from the kit’s proposed 60-minute flow (blue = fixed inputs).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="F5:F10">
+  <conditionalFormatting sqref="F5:F11">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(ISNUMBER(F5),F5&gt;3)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H5:H10">
+  <conditionalFormatting sqref="H5:H11">
     <cfRule type="expression" priority="2" dxfId="0">
       <formula>AND(ISNUMBER(H5),H5&gt;3)</formula>
     </cfRule>
@@ -2177,7 +2254,7 @@
       </c>
       <c r="C8" s="18" t="inlineStr">
         <is>
-          <t>“Let’s paste my real project status”</t>
+          <t>“Let’s paste my real project’s chat”</t>
         </is>
       </c>
       <c r="D8" s="18" t="inlineStr">
@@ -2333,7 +2410,7 @@
       </c>
       <c r="C14" s="18" t="inlineStr">
         <is>
-          <t>Report-out cut to 45 seconds</t>
+          <t>Debrief card cut to 45 seconds</t>
         </is>
       </c>
       <c r="D14" s="18" t="inlineStr">

--- a/ws2/files/WS2_Mock_Run_Scorecard.xlsx
+++ b/ws2/files/WS2_Mock_Run_Scorecard.xlsx
@@ -968,7 +968,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Card C3 The Silent Risk, given · experienced facilitator · 7–8 participants · approved tool available</t>
+          <t>Card C3 The Silent Risk, given · experienced facilitator · 7–8 participants · Builder with Agent Builder in Copilot Premium</t>
         </is>
       </c>
     </row>
